--- a/Data_Visualization/Column Line , Bar and Pie Chart.xlsx
+++ b/Data_Visualization/Column Line , Bar and Pie Chart.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\prana\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C3ADEB6-2FC9-41A3-AF96-20C57045B7EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA2C05FC-7A31-47F1-976E-5FF74584B301}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{8D6C3E24-154E-4CBF-9FDB-C2144009661E}"/>
   </bookViews>
@@ -1134,6 +1134,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-33A9-4887-8E59-EED4DD91D072}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -1153,6 +1158,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-33A9-4887-8E59-EED4DD91D072}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -1172,6 +1182,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-33A9-4887-8E59-EED4DD91D072}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
@@ -1191,6 +1206,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-33A9-4887-8E59-EED4DD91D072}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:spPr>
@@ -4890,7 +4910,7 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="42" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
